--- a/data/reports/pdca_history.xlsx
+++ b/data/reports/pdca_history.xlsx
@@ -9,10 +9,16 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily-science" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="scp-lab" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pokemon-lab" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yokai-watch" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2ch-matome" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$N$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$N$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$N$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$N$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$N$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$N$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$N$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1598,8 +1604,998 @@
         <v>0</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>47</v>
+      </c>
+      <c r="C23" t="n">
+        <v>139868</v>
+      </c>
+      <c r="D23" t="n">
+        <v>145</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>15</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>48</v>
+      </c>
+      <c r="C24" t="n">
+        <v>141876</v>
+      </c>
+      <c r="D24" t="n">
+        <v>146</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>15</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>48</v>
+      </c>
+      <c r="C25" t="n">
+        <v>141895</v>
+      </c>
+      <c r="D25" t="n">
+        <v>147</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>15</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>48</v>
+      </c>
+      <c r="C26" t="n">
+        <v>141895</v>
+      </c>
+      <c r="D26" t="n">
+        <v>151</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>15</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>48</v>
+      </c>
+      <c r="C27" t="n">
+        <v>141895</v>
+      </c>
+      <c r="D27" t="n">
+        <v>152</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>15</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>50</v>
+      </c>
+      <c r="C28" t="n">
+        <v>147000</v>
+      </c>
+      <c r="D28" t="n">
+        <v>155</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>体の不思議</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>15</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>50</v>
+      </c>
+      <c r="C29" t="n">
+        <v>150110</v>
+      </c>
+      <c r="D29" t="n">
+        <v>158</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>15</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>15</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>15</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>15</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>52</v>
+      </c>
+      <c r="C33" t="n">
+        <v>156535</v>
+      </c>
+      <c r="D33" t="n">
+        <v>166</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>15</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>52</v>
+      </c>
+      <c r="C34" t="n">
+        <v>160611</v>
+      </c>
+      <c r="D34" t="n">
+        <v>169</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>15</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>52</v>
+      </c>
+      <c r="C35" t="n">
+        <v>162426</v>
+      </c>
+      <c r="D35" t="n">
+        <v>170</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>15</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>53</v>
+      </c>
+      <c r="C36" t="n">
+        <v>163248</v>
+      </c>
+      <c r="D36" t="n">
+        <v>171</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>15</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>52</v>
+      </c>
+      <c r="C37" t="n">
+        <v>164131</v>
+      </c>
+      <c r="D37" t="n">
+        <v>172</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>15</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>52</v>
+      </c>
+      <c r="C38" t="n">
+        <v>165225</v>
+      </c>
+      <c r="D38" t="n">
+        <v>173</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>15</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>52</v>
+      </c>
+      <c r="C39" t="n">
+        <v>165989</v>
+      </c>
+      <c r="D39" t="n">
+        <v>174</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>15</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>15</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>52</v>
+      </c>
+      <c r="C41" t="n">
+        <v>167300</v>
+      </c>
+      <c r="D41" t="n">
+        <v>176</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>15</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N22"/>
+  <autoFilter ref="A1:N41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1610,7 +2606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2778,8 +3774,3532 @@
         <v>0</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>111</v>
+      </c>
+      <c r="C23" t="n">
+        <v>106836</v>
+      </c>
+      <c r="D23" t="n">
+        <v>118</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>15</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>112</v>
+      </c>
+      <c r="C24" t="n">
+        <v>108972</v>
+      </c>
+      <c r="D24" t="n">
+        <v>119</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>15</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>112</v>
+      </c>
+      <c r="C25" t="n">
+        <v>109003</v>
+      </c>
+      <c r="D25" t="n">
+        <v>120</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>対立組織・Kクラス</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>15</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>114</v>
+      </c>
+      <c r="C26" t="n">
+        <v>109003</v>
+      </c>
+      <c r="D26" t="n">
+        <v>122</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>対立組織・Kクラス</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>15</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>116</v>
+      </c>
+      <c r="C27" t="n">
+        <v>109003</v>
+      </c>
+      <c r="D27" t="n">
+        <v>123</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>対立組織・Kクラス</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>15</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>119</v>
+      </c>
+      <c r="C28" t="n">
+        <v>113465</v>
+      </c>
+      <c r="D28" t="n">
+        <v>126</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>15</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>122</v>
+      </c>
+      <c r="C29" t="n">
+        <v>116265</v>
+      </c>
+      <c r="D29" t="n">
+        <v>128</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>15</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>15</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>15</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>124</v>
+      </c>
+      <c r="C32" t="n">
+        <v>119353</v>
+      </c>
+      <c r="D32" t="n">
+        <v>132</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>15</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>126</v>
+      </c>
+      <c r="C33" t="n">
+        <v>121038</v>
+      </c>
+      <c r="D33" t="n">
+        <v>136</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>15</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>126</v>
+      </c>
+      <c r="C34" t="n">
+        <v>124637</v>
+      </c>
+      <c r="D34" t="n">
+        <v>138</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>15</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>126</v>
+      </c>
+      <c r="C35" t="n">
+        <v>125552</v>
+      </c>
+      <c r="D35" t="n">
+        <v>139</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>15</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>127</v>
+      </c>
+      <c r="C36" t="n">
+        <v>126650</v>
+      </c>
+      <c r="D36" t="n">
+        <v>140</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>15</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>127</v>
+      </c>
+      <c r="C37" t="n">
+        <v>127489</v>
+      </c>
+      <c r="D37" t="n">
+        <v>141</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>15</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>128</v>
+      </c>
+      <c r="C38" t="n">
+        <v>128621</v>
+      </c>
+      <c r="D38" t="n">
+        <v>142</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>15</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>15</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>15</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>131</v>
+      </c>
+      <c r="C41" t="n">
+        <v>130825</v>
+      </c>
+      <c r="D41" t="n">
+        <v>145</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>15</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N22"/>
+  <autoFilter ref="A1:N41"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>登録者数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>総再生数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>動画本数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>直近30日ショート本数</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>平均再生数</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>中央値再生数</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>平均いいね率</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>伸びてるジャンル</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>抑制候補ジャンル</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>テーマ重複ペア数</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>成功パターン分析(OK/NG)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>維持率分析(OK/NG)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>バズ続編投入数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>13827</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>15811</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>19138</v>
+      </c>
+      <c r="D12" t="n">
+        <v>15</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>22707</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>9</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>22758</v>
+      </c>
+      <c r="D14" t="n">
+        <v>17</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>9</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>24045</v>
+      </c>
+      <c r="D15" t="n">
+        <v>18</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>9</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" t="n">
+        <v>25712</v>
+      </c>
+      <c r="D16" t="n">
+        <v>19</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>9</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="n">
+        <v>27516</v>
+      </c>
+      <c r="D17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>9</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" t="n">
+        <v>28862</v>
+      </c>
+      <c r="D18" t="n">
+        <v>21</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>9</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>9</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>11</v>
+      </c>
+      <c r="C20" t="n">
+        <v>31967</v>
+      </c>
+      <c r="D20" t="n">
+        <v>22</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N20"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>登録者数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>総再生数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>動画本数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>直近30日ショート本数</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>平均再生数</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>中央値再生数</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>平均いいね率</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>伸びてるジャンル</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>抑制候補ジャンル</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>テーマ重複ペア数</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>成功パターン分析(OK/NG)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>維持率分析(OK/NG)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>バズ続編投入数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>9195</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10753</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>13919</v>
+      </c>
+      <c r="D12" t="n">
+        <v>14</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>18731</v>
+      </c>
+      <c r="D13" t="n">
+        <v>15</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>18774</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20718</v>
+      </c>
+      <c r="D15" t="n">
+        <v>17</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" t="n">
+        <v>22437</v>
+      </c>
+      <c r="D16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>24147</v>
+      </c>
+      <c r="D17" t="n">
+        <v>19</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>26424</v>
+      </c>
+      <c r="D18" t="n">
+        <v>20</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>6</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>28408</v>
+      </c>
+      <c r="D20" t="n">
+        <v>21</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>7</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N20"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>登録者数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>総再生数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>動画本数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>直近30日ショート本数</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>平均再生数</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>中央値再生数</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>平均いいね率</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>伸びてるジャンル</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>抑制候補ジャンル</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>テーマ重複ペア数</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>成功パターン分析(OK/NG)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>維持率分析(OK/NG)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>バズ続編投入数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1348</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1348</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1348</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1348</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2806</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10738</v>
+      </c>
+      <c r="D10" t="n">
+        <v>13</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/reports/pdca_history.xlsx
+++ b/data/reports/pdca_history.xlsx
@@ -12,13 +12,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pokemon-lab" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yokai-watch" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2ch-matome" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fake-paper" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$N$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$N$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$N$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$N$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$N$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'daily-science'!$A$1:$N$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'scp-lab'!$A$1:$N$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'pokemon-lab'!$A$1:$N$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'yokai-watch'!$A$1:$N$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2ch-matome'!$A$1:$N$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'fake-paper'!$A$1:$N$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2594,8 +2596,269 @@
         <v>0</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>52</v>
+      </c>
+      <c r="C42" t="n">
+        <v>168282</v>
+      </c>
+      <c r="D42" t="n">
+        <v>177</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>15</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>53</v>
+      </c>
+      <c r="C43" t="n">
+        <v>170470</v>
+      </c>
+      <c r="D43" t="n">
+        <v>181</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>15</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>53</v>
+      </c>
+      <c r="C44" t="n">
+        <v>172329</v>
+      </c>
+      <c r="D44" t="n">
+        <v>182</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>15</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>55</v>
+      </c>
+      <c r="C45" t="n">
+        <v>173839</v>
+      </c>
+      <c r="D45" t="n">
+        <v>183</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>15</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>睡眠・夢</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>宇宙・天体</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>15</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N41"/>
+  <autoFilter ref="A1:N46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2606,7 +2869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4764,8 +5027,269 @@
         <v>0</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>133</v>
+      </c>
+      <c r="C42" t="n">
+        <v>133388</v>
+      </c>
+      <c r="D42" t="n">
+        <v>146</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>15</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>134</v>
+      </c>
+      <c r="C43" t="n">
+        <v>134373</v>
+      </c>
+      <c r="D43" t="n">
+        <v>150</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>15</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>135</v>
+      </c>
+      <c r="C44" t="n">
+        <v>135406</v>
+      </c>
+      <c r="D44" t="n">
+        <v>152</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>15</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>135</v>
+      </c>
+      <c r="C45" t="n">
+        <v>136011</v>
+      </c>
+      <c r="D45" t="n">
+        <v>154</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>15</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>SCP個別オブジェクト</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>オブジェクトクラス</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>15</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N41"/>
+  <autoFilter ref="A1:N46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4776,7 +5300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5745,7 +6269,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
         <v>10</v>
       </c>
@@ -5763,8 +6286,245 @@
         <v>0</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>11</v>
+      </c>
+      <c r="C21" t="n">
+        <v>33937</v>
+      </c>
+      <c r="D21" t="n">
+        <v>23</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>13</v>
+      </c>
+      <c r="C22" t="n">
+        <v>36918</v>
+      </c>
+      <c r="D22" t="n">
+        <v>27</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>15</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>13</v>
+      </c>
+      <c r="C23" t="n">
+        <v>38852</v>
+      </c>
+      <c r="D23" t="n">
+        <v>28</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>15</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>13</v>
+      </c>
+      <c r="C24" t="n">
+        <v>40775</v>
+      </c>
+      <c r="D24" t="n">
+        <v>28</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>15</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>5</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N20"/>
+  <autoFilter ref="A1:N25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5775,7 +6535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6744,7 +7504,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
         <v>7</v>
       </c>
@@ -6762,8 +7521,245 @@
         <v>0</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" t="n">
+        <v>31792</v>
+      </c>
+      <c r="D21" t="n">
+        <v>22</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" t="n">
+        <v>34469</v>
+      </c>
+      <c r="D22" t="n">
+        <v>26</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>15</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" t="n">
+        <v>35799</v>
+      </c>
+      <c r="D23" t="n">
+        <v>27</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>15</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" t="n">
+        <v>36117</v>
+      </c>
+      <c r="D24" t="n">
+        <v>28</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>15</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>4</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N20"/>
+  <autoFilter ref="A1:N25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6774,7 +7770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7280,7 +8276,6 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
         <v>2</v>
       </c>
@@ -7298,8 +8293,531 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>14349</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>15</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>18291</v>
+      </c>
+      <c r="D12" t="n">
+        <v>22</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>20603</v>
+      </c>
+      <c r="D13" t="n">
+        <v>23</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>15</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>23644</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>15</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N10"/>
+  <autoFilter ref="A1:N15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>登録者数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>総再生数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>動画本数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>直近30日ショート本数</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>平均再生数</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>中央値再生数</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>平均いいね率</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>伸びてるジャンル</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>抑制候補ジャンル</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>テーマ重複ペア数</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>成功パターン分析(OK/NG)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>維持率分析(OK/NG)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>バズ続編投入数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1101</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1099</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>